--- a/01-03-02/check-form-blank.xlsx
+++ b/01-03-02/check-form-blank.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -591,44 +591,36 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>대표는 직원에게 맡기는 말로, 직장인은 상사·동료에게 넘기는 말로, 프리랜서는 거래처·외주에게 맡기는 말로 적어요. 실제로 했던 말 그대로 적어요(고쳐 쓰지 않기).</t>
+          <t>대표님이면 직원한테 맡기는 말로, 직장인이시면 상사나 동료한테 넘기는 말로, 프리랜서시면 거래처나 외주한테 맡기는 말로 적으시면 돼요. 평소에 했던 말 그대로 적어요.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>「있음」은 그 내용이 말 안에 들어 있을 때만이에요. 듣는 사람이 짐작해야 알 수 있으면 「없음」. AI에게는 그 짐작의 바탕인 우리 회사 맥락이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
+          <t>듣는 사람이 짐작해야 알 수 있는 건 빠진 걸로 세시면 돼요. AI에게는 그 짐작의 바탕인 우리 회사 맥락이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>매일 하는 손질처럼 마감이 따로 없는 일은 마감 칸을 「해당 없음」으로 두고 빠진 것에 세지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>빠진 칸을 채워 쓰는 법은 파트 3에서 해요. 지금은 표시만 해요.</t>
+          <t>빠진 칸이 많을수록 AI가 짐작할 게 많다는 뜻이고, 그만큼 다시 시키는 일도 늘어요. 채우는 법은 파트 3에서 하니까, 지금은 표시만 해 두세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B7:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"있음,없음,해당 없음"</formula1>
+      <formula1>"있음,없음"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -683,7 +675,7 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01-01-02 간소 진단서</t>
+          <t>AI 업무 시스템 진단 (레벨 등급 · 먼저 채울 칸)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -854,7 +846,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>괜찮다고 볼 판단 규칙. 릴스라면 좋아요·저장·댓글·공유 수, 프로필 링크로 넘어가 결제한 비율 같은 지표</t>
+          <t>괜찮다고 볼 판단 규칙. 공동구매라면 「상세페이지는 우리 브랜드 톤으로, 가격은 정가보다 높게 쓰지 않기」</t>
         </is>
       </c>
     </row>

--- a/01-03-02/check-form-blank.xlsx
+++ b/01-03-02/check-form-blank.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>가장 낮은 등급 · 그 영역 · 먼저 다질 칸</t>
+          <t>가장 낮은 등급 · 그 영역 · 먼저 채울 칸</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>첫 줄의 먼저 다질 칸 + 셋째 줄에서 빠진 칸을 한 줄로</t>
+          <t>첫 줄의 먼저 채울 칸 + 셋째 줄에서 빠진 칸을 한 줄로</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>컨설팅·교육에서 실제로 쓰는 말 (풀어 씀)</t>
+          <t>컨설팅·교육에서 실제로 쓰는 말</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>한 줄 정리: 다섯 가지를 다 넣어 두고 그대로 하게 하면 누가 와도 평균 이상이 나와요. 이걸 매번 말로 하지 않게 문서로 만든 게 파트 3에서 쓰는 업무 지시서예요.</t>
+          <t>한 줄 정리: 성공한 결과의 모습을 다 넣어 두고 그대로 하게 하면, 누가 와도 평균 이상은 나와요. 이걸 매번 말로 하지 않게 문서로 만든 게 파트 3에서 쓰는 업무 지시서예요.</t>
         </is>
       </c>
     </row>

--- a/01-03-02/check-form-blank.xlsx
+++ b/01-03-02/check-form-blank.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2장 지시 점검표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3장 파트 1 진단 한 장" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1장 다섯 가지" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1장 다섯 가지" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2장 지시 점검표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3장 파트 1 진단 한 장" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,11 +37,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -94,24 +94,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -479,6 +479,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>1장. 한마디에 빠진 다섯 가지</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>「인스타 릴스 하나 기획해서 가져와 봐」 같은 한마디에는 아래 다섯 가지가 빠져 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>다섯 가지</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>묻는 말</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>컨설팅·교육에서 실제로 쓰는 말</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1. 목적</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>왜 이 일을 하나?</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>이 공동구매를 왜 하는지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2. 결과물 모습</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>끝나면 어떤 모습이어야 하나?</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>청소가 끝나면 화이트보드는 비어 있고 컴퓨터는 꺼져 있는 것처럼, 끝난 상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3. 기준</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>무엇을 보면 잘됐다고 하나?</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>괜찮다고 볼 판단 규칙. 공동구매라면 「상세페이지는 우리 브랜드 톤으로, 가격은 정가보다 높게 쓰지 않기」</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4. 마감</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>언제까지, 얼마나 자주?</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>서명은 항상 하루 전까지처럼 기준과 주기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5. 참고 자료</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>무엇을 보고 하나?</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>참고 링크와 예시를 같이. 레퍼런스는 맡기는 쪽이 골라 줘요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>한 줄 정리: 성공한 결과의 모습을 다 넣어 두고 그대로 하게 하면, 누가 와도 평균 이상은 나와요. 이걸 매번 말로 하지 않게 문서로 만든 게 파트 3에서 쓰는 업무 지시서예요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -502,75 +649,75 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>내가 평소 일 시키는 말 한 줄</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="7" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>다섯 가지</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>내 말에 있나</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>왜 그렇게 봤나 (메모)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>1. 목적</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2. 결과물 모습</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>3. 기준</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>4. 마감</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>5. 참고 자료</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -579,7 +726,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(B7:B11,"없음")&amp;" / 5"</f>
+        <f>IF(COUNTA(B7:B11)=0,"",COUNTIF(B7:B11,"없음")&amp;" / 5")</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -627,7 +774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -656,238 +803,91 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>어디서</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>옮겨 적을 것</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>내 답</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>AI 업무 시스템 진단 (레벨 등급 · 먼저 채울 칸)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>가장 낮은 등급 · 그 영역 · 먼저 채울 칸</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>AI 업무 시스템 진단 (레벨 등급 · 지금 먼저 잡을 것)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>가장 낮은 등급 · 그 영역 · 지금 먼저 잡을 것</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>01-02-02 우선순위 표</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>★1 · ★2 · ★3</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>01-03-02 지시 점검표 (오늘)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>내 말 한 줄 · 빠진 것 __ / 5 · 빠진 칸 이름</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>01-03-01 한 줄 카드</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>나는 가·나·다 중 __에서 멈추는 사람 · 다음엔 __부터</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>나는 첫 번째 · 두 번째 · 세 번째 중 __에서 멈추는 사람 · 다음엔 __부터</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>한눈에 보이는 빈 곳</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>첫 줄의 먼저 채울 칸 + 셋째 줄에서 빠진 칸을 한 줄로</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>첫 줄의 지금 먼저 잡을 것 + 셋째 줄에서 빠진 칸을 한 줄로</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>이 빈 곳은 파트 2에서 비서가 일할 자리(자료 둘 곳·도구 연결)를 만들고, 파트 3에서 지시서로 채워 가요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>1장. 한마디에 빠진 다섯 가지</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>「인스타 릴스 좀 기획해서 가져와 봐」 같은 한마디에는 아래 다섯 가지가 빠져 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>다섯 가지</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>묻는 말</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>컨설팅·교육에서 실제로 쓰는 말</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>1. 목적</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>왜 이 일을 하나?</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>이 공동구매를 왜 하는지</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>2. 결과물 모습</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>끝나면 어떤 모습이어야 하나?</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>청소가 끝나면 화이트보드는 비어 있고 컴퓨터는 꺼져 있는 것처럼, 끝난 상태</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>3. 기준</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>무엇을 보면 잘됐다고 하나?</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>괜찮다고 볼 판단 규칙. 공동구매라면 「상세페이지는 우리 브랜드 톤으로, 가격은 정가보다 높게 쓰지 않기」</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>4. 마감</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>언제까지, 얼마나 자주?</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>서명은 항상 하루 전까지처럼 기준과 주기</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>5. 참고 자료</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>무엇을 보고 하나?</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>참고 링크와 예시를 같이. 레퍼런스는 맡기는 쪽이 골라 줘요</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>한 줄 정리: 성공한 결과의 모습을 다 넣어 두고 그대로 하게 하면, 누가 와도 평균 이상은 나와요. 이걸 매번 말로 하지 않게 문서로 만든 게 파트 3에서 쓰는 업무 지시서예요.</t>
         </is>
       </c>
     </row>

--- a/01-03-02/check-form-blank.xlsx
+++ b/01-03-02/check-form-blank.xlsx
@@ -62,7 +62,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -84,11 +84,44 @@
         <color rgb="00DCD1C1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DCD1C1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DCD1C1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DCD1C1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,6 +147,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +548,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>컨설팅·교육에서 실제로 쓰는 말</t>
+          <t>예를 들면</t>
         </is>
       </c>
     </row>
@@ -655,7 +689,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="7" t="n"/>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
